--- a/content/CO6930/CO6930 - definition (live).xlsx
+++ b/content/CO6930/CO6930 - definition (live).xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="TEMPLATE - definition" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="CO6930 - definition (live)" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -60,7 +60,7 @@
     <t>Trainer overview</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=9OaTz8f3sac</t>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=9OaTz8f3sac </t>
   </si>
   <si>
     <t>PDF</t>
@@ -69,7 +69,7 @@
     <t>PLC Fundamentals worksheets (PDF)</t>
   </si>
   <si>
-    <t>https://matrixtsl.github.io/IM6930/docs/CP2388%20%E2%80%93%20PLC%20Fundamentals%20for%20Maintenance%20Engineers.pdf</t>
+    <t xml:space="preserve">https://matrixtsl.github.io/IM6930/docs/CP2388%20%E2%80%93%20PLC%20Fundamentals%20for%20Maintenance%20Engineers.pdf </t>
   </si>
   <si>
     <t>Worksheet 1 – Simple PLC Systems</t>
@@ -81,7 +81,7 @@
     <t>Worksheet 2 overview</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=CPwaUnomzc8</t>
+    <t xml:space="preserve">https://www.youtube.com/watch?v=CPwaUnomzc8 </t>
   </si>
   <si>
     <t>Worksheet 2 – Complex PLC Systems</t>
@@ -166,7 +166,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -174,6 +174,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -192,11 +197,14 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -409,6 +417,11 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="27.0"/>
+    <col customWidth="1" min="4" max="4" width="38.13"/>
+    <col customWidth="1" min="5" max="5" width="101.63"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -491,7 +504,7 @@
       <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -508,7 +521,7 @@
       <c r="D6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -542,7 +555,7 @@
       <c r="D8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -768,6 +781,11 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="E5"/>
+    <hyperlink r:id="rId2" ref="E6"/>
+    <hyperlink r:id="rId3" ref="E8"/>
+  </hyperlinks>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>